--- a/data/trans_orig/P59A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P59A-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si viven actualmente en pareja en 2007</t>
+          <t>Población según si viven actualmente en pareja en 2007 (tasa de respuesta: 98,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>17367</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37350</t>
+          <t>37159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>8553</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24887</t>
+          <t>24764</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29345</t>
+          <t>28672</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53620</t>
+          <t>53996</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>222639</t>
+          <t>222830</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>243355</t>
+          <t>242622</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>234535</t>
+          <t>234658</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250039</t>
+          <t>250869</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>465792</t>
+          <t>465416</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>490067</t>
+          <t>490740</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31017</t>
+          <t>30046</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57831</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20561</t>
+          <t>21538</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43506</t>
+          <t>44325</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57935</t>
+          <t>59167</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91976</t>
+          <t>92966</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>304923</t>
+          <t>305529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>331737</t>
+          <t>332708</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>309387</t>
+          <t>308568</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>332332</t>
+          <t>331355</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>623671</t>
+          <t>622681</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>657712</t>
+          <t>656480</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23738</t>
+          <t>22398</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46288</t>
+          <t>44881</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20683</t>
+          <t>20848</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41960</t>
+          <t>40436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46342</t>
+          <t>48716</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77998</t>
+          <t>80356</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>188756</t>
+          <t>190163</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>211306</t>
+          <t>212646</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>224254</t>
+          <t>225778</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>245531</t>
+          <t>245366</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>423260</t>
+          <t>420902</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>454916</t>
+          <t>452542</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,28%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60531</t>
+          <t>61522</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91720</t>
+          <t>93214</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50438</t>
+          <t>51426</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81797</t>
+          <t>83531</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120878</t>
+          <t>120984</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163826</t>
+          <t>162922</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>338745</t>
+          <t>337251</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>369934</t>
+          <t>368943</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>421937</t>
+          <t>420203</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>453296</t>
+          <t>452308</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>770373</t>
+          <t>771277</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>813321</t>
+          <t>813215</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,05%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>151556</t>
+          <t>152374</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>204574</t>
+          <t>203455</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>118904</t>
+          <t>118514</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>164076</t>
+          <t>167653</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>281649</t>
+          <t>284463</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>352236</t>
+          <t>353780</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1083678</t>
+          <t>1084797</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1136696</t>
+          <t>1135878</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1218187</t>
+          <t>1214610</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1263359</t>
+          <t>1263749</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2318279</t>
+          <t>2316735</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2388866</t>
+          <t>2386052</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si viven actualmente en pareja en 2012</t>
+          <t>Población según si viven actualmente en pareja en 2012 (tasa de respuesta: 97,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26233</t>
+          <t>25919</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51601</t>
+          <t>51540</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21016</t>
+          <t>22574</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44209</t>
+          <t>45391</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53202</t>
+          <t>51756</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87182</t>
+          <t>86257</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>221285</t>
+          <t>221346</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246653</t>
+          <t>246967</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>208632</t>
+          <t>207450</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>231825</t>
+          <t>230267</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>438545</t>
+          <t>439470</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>472525</t>
+          <t>473971</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,16%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47811</t>
+          <t>47388</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79001</t>
+          <t>78902</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37268</t>
+          <t>37130</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65614</t>
+          <t>64958</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91585</t>
+          <t>92652</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>133212</t>
+          <t>133244</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>320997</t>
+          <t>321096</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>352187</t>
+          <t>352610</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324519</t>
+          <t>325175</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>352865</t>
+          <t>353003</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>656919</t>
+          <t>656887</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>698546</t>
+          <t>697479</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,27%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43390</t>
+          <t>43139</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72218</t>
+          <t>72275</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31406</t>
+          <t>31655</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57001</t>
+          <t>56858</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79856</t>
+          <t>80047</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119817</t>
+          <t>118353</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>236195</t>
+          <t>236138</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>265023</t>
+          <t>265274</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>244119</t>
+          <t>244262</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>269714</t>
+          <t>269465</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>489717</t>
+          <t>491181</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>529678</t>
+          <t>529487</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,87%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43074</t>
+          <t>43545</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71652</t>
+          <t>70315</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62800</t>
+          <t>63765</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98936</t>
+          <t>98303</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114298</t>
+          <t>112786</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>159613</t>
+          <t>157941</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>330391</t>
+          <t>331728</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358969</t>
+          <t>358498</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>380753</t>
+          <t>381386</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>416889</t>
+          <t>415924</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>722118</t>
+          <t>723790</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>767433</t>
+          <t>768945</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,21%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>187924</t>
+          <t>185313</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>245821</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>177179</t>
+          <t>176522</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>229468</t>
+          <t>230592</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>374364</t>
+          <t>375886</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>452819</t>
+          <t>456788</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1137519</t>
+          <t>1141846</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1195416</t>
+          <t>1198027</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1194315</t>
+          <t>1193191</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1246604</t>
+          <t>1247261</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2354304</t>
+          <t>2350335</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2432759</t>
+          <t>2431237</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,61%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si viven actualmente en pareja en 2016</t>
+          <t>Población según si viven actualmente en pareja en 2016 (tasa de respuesta: 97,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37712</t>
+          <t>37286</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63394</t>
+          <t>63395</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27253</t>
+          <t>27027</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48911</t>
+          <t>48843</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68561</t>
+          <t>69882</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102304</t>
+          <t>104543</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>223119</t>
+          <t>223118</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>248801</t>
+          <t>249227</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>228903</t>
+          <t>228971</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250561</t>
+          <t>250787</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>462023</t>
+          <t>459784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>495766</t>
+          <t>494445</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,62%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56980</t>
+          <t>58563</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91854</t>
+          <t>92867</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48954</t>
+          <t>49137</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78230</t>
+          <t>79135</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115347</t>
+          <t>115632</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159227</t>
+          <t>162081</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>348911</t>
+          <t>347898</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>383785</t>
+          <t>382202</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>320453</t>
+          <t>319548</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>349729</t>
+          <t>349546</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>680221</t>
+          <t>677367</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>724101</t>
+          <t>723816</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,23%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41479</t>
+          <t>41679</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69563</t>
+          <t>68830</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36120</t>
+          <t>36655</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60801</t>
+          <t>63194</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84181</t>
+          <t>85731</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123367</t>
+          <t>124814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>251985</t>
+          <t>252718</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>280069</t>
+          <t>279869</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>294591</t>
+          <t>292198</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>319272</t>
+          <t>318737</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>553573</t>
+          <t>552126</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>592759</t>
+          <t>591209</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,34%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62032</t>
+          <t>61758</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94371</t>
+          <t>94750</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60760</t>
+          <t>61892</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94011</t>
+          <t>96028</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>130377</t>
+          <t>133178</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176922</t>
+          <t>178293</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>318746</t>
+          <t>318367</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>351085</t>
+          <t>351359</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>467216</t>
+          <t>465199</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>500467</t>
+          <t>499335</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>797422</t>
+          <t>796051</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>843967</t>
+          <t>841166</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,33%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>227296</t>
+          <t>227067</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>286069</t>
+          <t>287809</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>197988</t>
+          <t>197057</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>253637</t>
+          <t>255272</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>438777</t>
+          <t>441393</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>521238</t>
+          <t>522749</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1175873</t>
+          <t>1174133</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1234646</t>
+          <t>1234875</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1339478</t>
+          <t>1337843</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1395127</t>
+          <t>1396058</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2533820</t>
+          <t>2532309</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2616281</t>
+          <t>2613665</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,55%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si viven actualmente en pareja en 2023</t>
+          <t>Población según si viven actualmente en pareja en 2023 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30506</t>
+          <t>30572</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62433</t>
+          <t>61242</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28205</t>
+          <t>28184</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49109</t>
+          <t>49579</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64238</t>
+          <t>63802</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101429</t>
+          <t>100228</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>280748</t>
+          <t>281939</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>312675</t>
+          <t>312609</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270433</t>
+          <t>269963</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>291337</t>
+          <t>291358</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>561294</t>
+          <t>562495</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>598485</t>
+          <t>598921</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,37%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57683</t>
+          <t>58449</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>99436</t>
+          <t>101732</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54668</t>
+          <t>55008</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85215</t>
+          <t>86559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122288</t>
+          <t>122578</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>174848</t>
+          <t>172769</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369177</t>
+          <t>366881</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>410930</t>
+          <t>410164</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351599</t>
+          <t>350255</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>382146</t>
+          <t>381806</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>730579</t>
+          <t>732658</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>783139</t>
+          <t>782849</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,46%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50793</t>
+          <t>50023</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85856</t>
+          <t>88353</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45946</t>
+          <t>46742</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74896</t>
+          <t>76058</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103398</t>
+          <t>104266</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>150806</t>
+          <t>150683</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>260974</t>
+          <t>258477</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>296037</t>
+          <t>296807</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>267601</t>
+          <t>266439</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>296551</t>
+          <t>295755</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>538521</t>
+          <t>538644</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>585929</t>
+          <t>585061</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56120</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89587</t>
+          <t>90547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42642</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81604</t>
+          <t>81550</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107384</t>
+          <t>106981</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162492</t>
+          <t>159858</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>381377</t>
+          <t>380417</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>414844</t>
+          <t>415291</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>571732</t>
+          <t>571786</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>610694</t>
+          <t>610143</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>961808</t>
+          <t>964442</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1016916</t>
+          <t>1017319</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,48%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>224744</t>
+          <t>223772</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>295040</t>
+          <t>297705</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>193613</t>
+          <t>195437</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>261573</t>
+          <t>260487</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>440373</t>
+          <t>439869</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>543579</t>
+          <t>536616</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1334548</t>
+          <t>1331883</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1404844</t>
+          <t>1405816</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1490616</t>
+          <t>1491702</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1558576</t>
+          <t>1556752</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2838198</t>
+          <t>2845161</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2941404</t>
+          <t>2941908</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P59A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P59A-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17367</t>
+          <t>16198</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37159</t>
+          <t>35793</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>8951</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24764</t>
+          <t>24633</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28672</t>
+          <t>29153</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53996</t>
+          <t>55320</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>222830</t>
+          <t>224196</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>242622</t>
+          <t>243791</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>234658</t>
+          <t>234789</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250869</t>
+          <t>250471</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>465416</t>
+          <t>464092</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>490740</t>
+          <t>490259</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>30572</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57225</t>
+          <t>58105</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21538</t>
+          <t>21688</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44325</t>
+          <t>44239</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59167</t>
+          <t>58322</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92966</t>
+          <t>92988</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>305529</t>
+          <t>304649</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>332708</t>
+          <t>332182</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>308568</t>
+          <t>308654</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>331355</t>
+          <t>331205</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>622681</t>
+          <t>622659</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>656480</t>
+          <t>657325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22398</t>
+          <t>22637</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>46613</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20848</t>
+          <t>20326</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40436</t>
+          <t>40894</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48716</t>
+          <t>48193</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80356</t>
+          <t>78588</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>190163</t>
+          <t>188431</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>212646</t>
+          <t>212407</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>225778</t>
+          <t>225320</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>245366</t>
+          <t>245888</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>420902</t>
+          <t>422670</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>452542</t>
+          <t>453065</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,39%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61522</t>
+          <t>60104</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93214</t>
+          <t>92815</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51426</t>
+          <t>50892</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83531</t>
+          <t>82101</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120984</t>
+          <t>122666</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162922</t>
+          <t>166206</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>337251</t>
+          <t>337650</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368943</t>
+          <t>370361</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>420203</t>
+          <t>421633</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>452308</t>
+          <t>452842</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>771277</t>
+          <t>767993</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>813215</t>
+          <t>811533</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,87%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>152374</t>
+          <t>152328</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>203455</t>
+          <t>203813</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>118514</t>
+          <t>119166</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>167653</t>
+          <t>166694</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>284463</t>
+          <t>284529</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>353780</t>
+          <t>357341</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1084797</t>
+          <t>1084439</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1135878</t>
+          <t>1135924</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1214610</t>
+          <t>1215569</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1263749</t>
+          <t>1263097</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2316735</t>
+          <t>2313174</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2386052</t>
+          <t>2385986</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25919</t>
+          <t>27086</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51540</t>
+          <t>52380</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22574</t>
+          <t>21030</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45391</t>
+          <t>44121</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51756</t>
+          <t>54835</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86257</t>
+          <t>85915</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>221346</t>
+          <t>220506</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246967</t>
+          <t>245800</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>207450</t>
+          <t>208720</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>230267</t>
+          <t>231811</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>439470</t>
+          <t>439812</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>473971</t>
+          <t>470892</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,57%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47388</t>
+          <t>47735</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78902</t>
+          <t>77469</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37130</t>
+          <t>37390</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64958</t>
+          <t>66376</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92652</t>
+          <t>91733</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>133244</t>
+          <t>132104</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>321096</t>
+          <t>322529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>352610</t>
+          <t>352263</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>325175</t>
+          <t>323757</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>353003</t>
+          <t>352743</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>656887</t>
+          <t>658027</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>697479</t>
+          <t>698398</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,39%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43139</t>
+          <t>43606</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72275</t>
+          <t>74034</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31655</t>
+          <t>32177</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56858</t>
+          <t>57875</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80047</t>
+          <t>81185</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118353</t>
+          <t>121344</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>236138</t>
+          <t>234379</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>265274</t>
+          <t>264807</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>244262</t>
+          <t>243245</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>269465</t>
+          <t>268943</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>491181</t>
+          <t>488190</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>529487</t>
+          <t>528349</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,68%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43545</t>
+          <t>43721</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70315</t>
+          <t>70700</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63765</t>
+          <t>63949</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98303</t>
+          <t>98157</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112786</t>
+          <t>113874</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157941</t>
+          <t>158142</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>331728</t>
+          <t>331343</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358498</t>
+          <t>358322</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>381386</t>
+          <t>381532</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>415924</t>
+          <t>415740</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>723790</t>
+          <t>723589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>768945</t>
+          <t>767857</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,09%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>185313</t>
+          <t>184121</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>241494</t>
+          <t>238355</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>176522</t>
+          <t>174290</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>230592</t>
+          <t>233501</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>375886</t>
+          <t>373746</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>456788</t>
+          <t>452634</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1141846</t>
+          <t>1144985</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1198027</t>
+          <t>1199219</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1193191</t>
+          <t>1190282</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1247261</t>
+          <t>1249493</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2350335</t>
+          <t>2354489</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2431237</t>
+          <t>2433377</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,69%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37286</t>
+          <t>37363</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63395</t>
+          <t>64659</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27027</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48843</t>
+          <t>48942</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69882</t>
+          <t>70362</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104543</t>
+          <t>104443</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>223118</t>
+          <t>221854</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>249227</t>
+          <t>249150</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>228971</t>
+          <t>228872</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250787</t>
+          <t>251326</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>459784</t>
+          <t>459884</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>494445</t>
+          <t>493965</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,53%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58563</t>
+          <t>58214</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92867</t>
+          <t>92777</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49137</t>
+          <t>48967</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79135</t>
+          <t>79103</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115632</t>
+          <t>116787</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>162081</t>
+          <t>162342</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>347898</t>
+          <t>347988</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>382202</t>
+          <t>382551</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>319548</t>
+          <t>319580</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>349546</t>
+          <t>349716</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>677367</t>
+          <t>677106</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>723816</t>
+          <t>722661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41679</t>
+          <t>41211</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68830</t>
+          <t>70093</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36655</t>
+          <t>37276</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63194</t>
+          <t>62910</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85731</t>
+          <t>84632</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>124814</t>
+          <t>122057</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>252718</t>
+          <t>251455</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>279869</t>
+          <t>280337</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>292198</t>
+          <t>292482</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>318737</t>
+          <t>318116</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>552126</t>
+          <t>554883</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>591209</t>
+          <t>592308</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,5%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61758</t>
+          <t>62040</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94750</t>
+          <t>92510</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61892</t>
+          <t>59771</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96028</t>
+          <t>93117</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133178</t>
+          <t>131485</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>178293</t>
+          <t>178654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>318367</t>
+          <t>320607</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>351359</t>
+          <t>351077</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>465199</t>
+          <t>468110</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>499335</t>
+          <t>501456</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>796051</t>
+          <t>795690</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>841166</t>
+          <t>842859</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,51%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>227067</t>
+          <t>226086</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>287809</t>
+          <t>284564</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>197057</t>
+          <t>196240</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>255272</t>
+          <t>254437</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>441393</t>
+          <t>439242</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>522749</t>
+          <t>521488</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1174133</t>
+          <t>1177378</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1234875</t>
+          <t>1235856</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1337843</t>
+          <t>1338678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1396058</t>
+          <t>1396875</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2532309</t>
+          <t>2533570</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2613665</t>
+          <t>2615816</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>43239</t>
+          <t>47408</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30572</t>
+          <t>32886</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61242</t>
+          <t>65237</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>37779</t>
+          <t>41982</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28184</t>
+          <t>30759</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49579</t>
+          <t>55396</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>81018</t>
+          <t>89390</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63802</t>
+          <t>72096</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100228</t>
+          <t>111965</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>299942</t>
+          <t>313355</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281939</t>
+          <t>295526</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>312609</t>
+          <t>327877</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>281763</t>
+          <t>304823</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269963</t>
+          <t>291409</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>291358</t>
+          <t>316046</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>581705</t>
+          <t>618177</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>562495</t>
+          <t>595602</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>598921</t>
+          <t>635471</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>343181</t>
+          <t>360763</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>343181</t>
+          <t>360763</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>343181</t>
+          <t>360763</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>319542</t>
+          <t>346805</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>319542</t>
+          <t>346805</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>319542</t>
+          <t>346805</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>662723</t>
+          <t>707567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>662723</t>
+          <t>707567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>662723</t>
+          <t>707567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77364</t>
+          <t>84886</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58449</t>
+          <t>63706</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101732</t>
+          <t>107376</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68308</t>
+          <t>75878</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55008</t>
+          <t>60770</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86559</t>
+          <t>93422</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>145672</t>
+          <t>160764</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122578</t>
+          <t>134768</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172769</t>
+          <t>188130</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>391249</t>
+          <t>422159</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>366881</t>
+          <t>399669</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>410164</t>
+          <t>443339</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>368506</t>
+          <t>417113</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>350255</t>
+          <t>399569</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>381806</t>
+          <t>432221</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>759755</t>
+          <t>839272</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>732658</t>
+          <t>811906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>782849</t>
+          <t>865268</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,52%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>468613</t>
+          <t>507045</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>468613</t>
+          <t>507045</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>468613</t>
+          <t>507045</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>436814</t>
+          <t>492991</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>436814</t>
+          <t>492991</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>436814</t>
+          <t>492991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>905427</t>
+          <t>1000036</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>905427</t>
+          <t>1000036</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>905427</t>
+          <t>1000036</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>67031</t>
+          <t>74518</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50023</t>
+          <t>56886</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88353</t>
+          <t>97296</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>59283</t>
+          <t>67861</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46742</t>
+          <t>53818</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76058</t>
+          <t>82997</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>126314</t>
+          <t>142380</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>104266</t>
+          <t>119995</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>150683</t>
+          <t>170144</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>279799</t>
+          <t>307960</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>258477</t>
+          <t>285182</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>296807</t>
+          <t>325592</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>283214</t>
+          <t>330831</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>266439</t>
+          <t>315695</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>295755</t>
+          <t>344874</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>563013</t>
+          <t>638790</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>538644</t>
+          <t>611026</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>585061</t>
+          <t>661175</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,64%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>346830</t>
+          <t>382478</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>346830</t>
+          <t>382478</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>346830</t>
+          <t>382478</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>342497</t>
+          <t>398692</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>342497</t>
+          <t>398692</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>342497</t>
+          <t>398692</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>689327</t>
+          <t>781170</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>689327</t>
+          <t>781170</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>689327</t>
+          <t>781170</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>70872</t>
+          <t>78385</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>59186</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90547</t>
+          <t>96810</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>63629</t>
+          <t>71966</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>57998</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81550</t>
+          <t>89483</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>134500</t>
+          <t>150351</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106981</t>
+          <t>126482</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>159858</t>
+          <t>173941</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>400092</t>
+          <t>420356</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>380417</t>
+          <t>401931</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>415291</t>
+          <t>439555</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>589707</t>
+          <t>560793</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>571786</t>
+          <t>543276</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>610143</t>
+          <t>574761</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>989800</t>
+          <t>981149</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>964442</t>
+          <t>957559</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1017319</t>
+          <t>1005018</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>88,82%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>470964</t>
+          <t>498741</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>470964</t>
+          <t>498741</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>470964</t>
+          <t>498741</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>653336</t>
+          <t>632759</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>653336</t>
+          <t>632759</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>653336</t>
+          <t>632759</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1124300</t>
+          <t>1131500</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1124300</t>
+          <t>1131500</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1124300</t>
+          <t>1131500</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>258506</t>
+          <t>285198</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>223772</t>
+          <t>249020</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>297705</t>
+          <t>325349</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>228998</t>
+          <t>257687</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>195437</t>
+          <t>228445</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>260487</t>
+          <t>283176</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>487504</t>
+          <t>542885</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>439869</t>
+          <t>499586</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>536616</t>
+          <t>595084</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1371082</t>
+          <t>1463829</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1331883</t>
+          <t>1423678</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1405816</t>
+          <t>1500007</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1523191</t>
+          <t>1613560</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1491702</t>
+          <t>1588071</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1556752</t>
+          <t>1642802</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2894273</t>
+          <t>3077389</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2845161</t>
+          <t>3025190</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2941908</t>
+          <t>3120688</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,2%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1629588</t>
+          <t>1749027</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1629588</t>
+          <t>1749027</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1629588</t>
+          <t>1749027</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1752189</t>
+          <t>1871247</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1752189</t>
+          <t>1871247</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1752189</t>
+          <t>1871247</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3381777</t>
+          <t>3620274</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3381777</t>
+          <t>3620274</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3381777</t>
+          <t>3620274</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
